--- a/research/traditional_assets/database/data/israel/israel_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_insurance_general.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1265</v>
+        <v>-0.03635</v>
       </c>
       <c r="E2">
-        <v>0.2645</v>
+        <v>0.0478</v>
       </c>
       <c r="G2">
-        <v>0.0498918688038127</v>
+        <v>0.1922643084350396</v>
       </c>
       <c r="H2">
-        <v>0.0498918688038127</v>
+        <v>0.1922643084350396</v>
       </c>
       <c r="I2">
-        <v>0.07802303313434901</v>
+        <v>0.1264660825878757</v>
       </c>
       <c r="J2">
-        <v>0.05562639201845226</v>
+        <v>0.08805010807863882</v>
       </c>
       <c r="K2">
-        <v>1986.8</v>
+        <v>1339.9</v>
       </c>
       <c r="L2">
-        <v>0.04466425375986332</v>
+        <v>0.07556906625758568</v>
       </c>
       <c r="M2">
-        <v>357.47</v>
+        <v>448.7691</v>
       </c>
       <c r="N2">
-        <v>0.03073847318004368</v>
+        <v>0.05140833953834698</v>
       </c>
       <c r="O2">
-        <v>0.1799224884235957</v>
+        <v>0.3349273080080603</v>
       </c>
       <c r="P2">
-        <v>300.9</v>
+        <v>384.6691</v>
       </c>
       <c r="Q2">
-        <v>0.02587407776841454</v>
+        <v>0.04406542184546652</v>
       </c>
       <c r="R2">
-        <v>0.1514495671431448</v>
+        <v>0.287087917008732</v>
       </c>
       <c r="S2">
-        <v>56.56999999999999</v>
+        <v>64.09999999999998</v>
       </c>
       <c r="T2">
-        <v>0.1582510420454863</v>
+        <v>0.1428351461809647</v>
       </c>
       <c r="U2">
-        <v>18454.1</v>
+        <v>17549.1</v>
       </c>
       <c r="V2">
-        <v>1.586848848607839</v>
+        <v>2.010321324245375</v>
       </c>
       <c r="W2">
-        <v>0.2178552839071821</v>
+        <v>0.1070552992838105</v>
       </c>
       <c r="X2">
-        <v>0.07191861245797365</v>
+        <v>0.1300555468841647</v>
       </c>
       <c r="Y2">
-        <v>0.1459366714492084</v>
+        <v>-0.02300024760035416</v>
       </c>
       <c r="Z2">
-        <v>6.033878251731592</v>
+        <v>2.695028941919304</v>
       </c>
       <c r="AA2">
-        <v>0.2610996550983268</v>
+        <v>0.1511248825181818</v>
       </c>
       <c r="AB2">
-        <v>0.04959057681121611</v>
+        <v>0.07913219930949948</v>
       </c>
       <c r="AC2">
-        <v>0.2123589299792741</v>
+        <v>0.07137575426369175</v>
       </c>
       <c r="AD2">
-        <v>11252.8</v>
+        <v>13350.4</v>
       </c>
       <c r="AE2">
-        <v>33.00708542376566</v>
+        <v>29.77591425446982</v>
       </c>
       <c r="AF2">
-        <v>11285.80708542376</v>
+        <v>13380.17591425447</v>
       </c>
       <c r="AG2">
-        <v>-7168.292914576234</v>
+        <v>-4168.924085745528</v>
       </c>
       <c r="AH2">
-        <v>0.4925029498250794</v>
+        <v>0.6051728648644756</v>
       </c>
       <c r="AI2">
-        <v>0.4660204556835727</v>
+        <v>0.5214557089984521</v>
       </c>
       <c r="AJ2">
-        <v>-1.606841704831057</v>
+        <v>-0.9141222872127174</v>
       </c>
       <c r="AK2">
-        <v>-1.243781184713526</v>
+        <v>-0.5140362095498092</v>
       </c>
       <c r="AL2">
-        <v>424.73</v>
+        <v>527.76</v>
       </c>
       <c r="AM2">
-        <v>424.73</v>
+        <v>527.76</v>
       </c>
       <c r="AN2">
-        <v>3.093782906222592</v>
+        <v>5.530176877511288</v>
       </c>
       <c r="AO2">
-        <v>8.15435688555082</v>
+        <v>4.234879490677581</v>
       </c>
       <c r="AP2">
-        <v>-1.970811005786336</v>
+        <v>-1.72690612888676</v>
       </c>
       <c r="AQ2">
-        <v>8.15435688555082</v>
+        <v>4.234879490677581</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Phoenix Holdings Ltd. (TASE:PHOE)</t>
+          <t>Clal Insurance Enterprises Holdings Ltd. (TASE:CLIS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,109 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.175</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="E3">
-        <v>0.312</v>
+        <v>-0.04769999999999999</v>
       </c>
       <c r="G3">
-        <v>0.06602911344434785</v>
+        <v>0.189383504115572</v>
       </c>
       <c r="H3">
-        <v>0.06602911344434785</v>
+        <v>0.189383504115572</v>
       </c>
       <c r="I3">
-        <v>0.1043936091882618</v>
+        <v>0.07223248782126659</v>
       </c>
       <c r="J3">
-        <v>0.0740290098207515</v>
+        <v>0.05217028942343113</v>
       </c>
       <c r="K3">
-        <v>619.7</v>
+        <v>120.1</v>
       </c>
       <c r="L3">
-        <v>0.06907198109632405</v>
+        <v>0.04034940366201915</v>
       </c>
       <c r="M3">
-        <v>148.7</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.04546844422700587</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.2399548168468613</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>117.8</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03602005870841487</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.1900919799903179</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>30.89999999999999</v>
-      </c>
-      <c r="T3">
-        <v>0.2078009414929388</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>4649</v>
+        <v>3906.4</v>
       </c>
       <c r="V3">
-        <v>1.421538649706458</v>
+        <v>3.138174807197944</v>
       </c>
       <c r="W3">
-        <v>0.2975464541220532</v>
+        <v>0.05294013929295601</v>
       </c>
       <c r="X3">
-        <v>0.06549279962396216</v>
+        <v>0.1576888399371946</v>
       </c>
       <c r="Y3">
-        <v>0.232053654498091</v>
-      </c>
-      <c r="Z3">
-        <v>41.53474865141113</v>
-      </c>
-      <c r="AA3">
-        <v>3.07477631581776</v>
+        <v>-0.1047487006442386</v>
       </c>
       <c r="AB3">
-        <v>0.04870880671745382</v>
-      </c>
-      <c r="AC3">
-        <v>3.026067509100306</v>
+        <v>0.07845188888337687</v>
       </c>
       <c r="AD3">
-        <v>2068.3</v>
+        <v>2787.3</v>
       </c>
       <c r="AE3">
-        <v>33.00708542376566</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>2101.307085423766</v>
+        <v>2787.3</v>
       </c>
       <c r="AG3">
-        <v>-2547.692914576234</v>
+        <v>-1119.1</v>
       </c>
       <c r="AH3">
-        <v>0.391180504075828</v>
+        <v>0.6912774980779246</v>
       </c>
       <c r="AI3">
-        <v>0.4201347812837752</v>
+        <v>0.5525204670247983</v>
       </c>
       <c r="AJ3">
-        <v>-3.52520815965485</v>
+        <v>-8.902943516308667</v>
       </c>
       <c r="AK3">
-        <v>-7.227352356658394</v>
+        <v>-0.983132741807959</v>
       </c>
       <c r="AL3">
-        <v>61.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AM3">
-        <v>61.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AN3">
-        <v>2.132927709600908</v>
+        <v>12.33318584070797</v>
       </c>
       <c r="AO3">
-        <v>15.18464052287582</v>
+        <v>3.111432706222866</v>
       </c>
       <c r="AP3">
-        <v>-2.627300107843905</v>
+        <v>-4.951769911504424</v>
       </c>
       <c r="AQ3">
-        <v>15.18464052287582</v>
+        <v>3.111432706222866</v>
       </c>
     </row>
     <row r="4">
@@ -856,115 +844,112 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.175</v>
+        <v>-0.122</v>
+      </c>
+      <c r="E4">
+        <v>0.0478</v>
       </c>
       <c r="G4">
-        <v>0.02642949187659499</v>
+        <v>0.2365327195819856</v>
       </c>
       <c r="H4">
-        <v>0.02642949187659499</v>
+        <v>0.2365327195819856</v>
       </c>
       <c r="I4">
-        <v>0.06172777118023094</v>
+        <v>0.1429149042050261</v>
       </c>
       <c r="J4">
-        <v>0.04012960839270446</v>
+        <v>0.09471240046955132</v>
       </c>
       <c r="K4">
-        <v>397.2</v>
+        <v>257</v>
       </c>
       <c r="L4">
-        <v>0.0334537736564166</v>
+        <v>0.07993281910923115</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>13.2</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.01099725068732817</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.05136186770428015</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>13.2</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.01099725068732817</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.05136186770428015</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>5391.7</v>
+        <v>5076</v>
       </c>
       <c r="V4">
-        <v>3.097254136029412</v>
+        <v>4.228942764308923</v>
       </c>
       <c r="W4">
-        <v>0.214923434879065</v>
+        <v>0.1055484824838802</v>
       </c>
       <c r="X4">
-        <v>0.07674703427752688</v>
+        <v>0.1441282921248558</v>
       </c>
       <c r="Y4">
-        <v>0.1381764006015381</v>
-      </c>
-      <c r="Z4">
-        <v>52.76933333333334</v>
-      </c>
-      <c r="AA4">
-        <v>2.117612681810753</v>
+        <v>-0.03857980964097554</v>
       </c>
       <c r="AB4">
-        <v>0.05051782003580456</v>
-      </c>
-      <c r="AC4">
-        <v>2.067094861774948</v>
+        <v>0.07870551215950414</v>
       </c>
       <c r="AD4">
-        <v>1873.2</v>
+        <v>2203.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1873.2</v>
+        <v>2203.3</v>
       </c>
       <c r="AG4">
-        <v>-3518.5</v>
+        <v>-2872.7</v>
       </c>
       <c r="AH4">
-        <v>0.5183176535694521</v>
+        <v>0.6473439887178282</v>
       </c>
       <c r="AI4">
-        <v>0.4345970024592827</v>
+        <v>0.5044415953111406</v>
       </c>
       <c r="AJ4">
-        <v>1.979242841874332</v>
+        <v>1.717711073905764</v>
       </c>
       <c r="AK4">
-        <v>3.25335182616736</v>
+        <v>4.056340016944366</v>
       </c>
       <c r="AL4">
-        <v>52.4</v>
+        <v>68.5</v>
       </c>
       <c r="AM4">
-        <v>52.4</v>
+        <v>68.5</v>
       </c>
       <c r="AN4">
-        <v>2.461821527138915</v>
+        <v>4.523301170190926</v>
       </c>
       <c r="AO4">
-        <v>13.98664122137404</v>
+        <v>6.708029197080292</v>
       </c>
       <c r="AP4">
-        <v>-4.624129320541464</v>
+        <v>-5.897556969821391</v>
       </c>
       <c r="AQ4">
-        <v>13.98664122137404</v>
+        <v>6.708029197080292</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clal Insurance Enterprises Holdings Ltd. (TASE:CLIS)</t>
+          <t>The Phoenix Holdings Ltd. (TASE:PHOE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,115 +969,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.172</v>
+        <v>-0.0438</v>
+      </c>
+      <c r="E5">
+        <v>0.129</v>
       </c>
       <c r="G5">
-        <v>0.03277882286402813</v>
+        <v>0.2680613582995334</v>
       </c>
       <c r="H5">
-        <v>0.03277882286402813</v>
+        <v>0.2680613582995334</v>
       </c>
       <c r="I5">
-        <v>0.0761683449522334</v>
+        <v>0.2030876817264207</v>
       </c>
       <c r="J5">
-        <v>0.0515627256139352</v>
+        <v>0.1520474608138278</v>
       </c>
       <c r="K5">
-        <v>362.4</v>
+        <v>459.1</v>
       </c>
       <c r="L5">
-        <v>0.04455755966212976</v>
+        <v>0.1400079290049099</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>235</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.0878603207836393</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.511871052058375</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>219.3</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.08199050360788127</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.4776737094314964</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>15.69999999999999</v>
+      </c>
+      <c r="T5">
+        <v>0.06680851063829782</v>
       </c>
       <c r="U5">
-        <v>4319.2</v>
+        <v>5131.1</v>
       </c>
       <c r="V5">
-        <v>2.485441362642421</v>
+        <v>1.918383370097581</v>
       </c>
       <c r="W5">
-        <v>0.2207871329352991</v>
+        <v>0.1630326704545455</v>
       </c>
       <c r="X5">
-        <v>0.07404666140580966</v>
+        <v>0.1120416397094843</v>
       </c>
       <c r="Y5">
-        <v>0.1467404715294894</v>
+        <v>0.0509910307450612</v>
       </c>
       <c r="Z5">
-        <v>7.085373290356304</v>
+        <v>12.37041852415191</v>
       </c>
       <c r="AA5">
-        <v>0.3653411588429474</v>
+        <v>1.880890725801639</v>
       </c>
       <c r="AB5">
-        <v>0.05043426590466184</v>
+        <v>0.0797390475895102</v>
       </c>
       <c r="AC5">
-        <v>0.3149068929382856</v>
+        <v>1.801151678212128</v>
       </c>
       <c r="AD5">
-        <v>1689.2</v>
+        <v>2326.1</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>29.77591425446982</v>
       </c>
       <c r="AF5">
-        <v>1689.2</v>
+        <v>2355.87591425447</v>
       </c>
       <c r="AG5">
-        <v>-2630</v>
+        <v>-2775.224085745531</v>
       </c>
       <c r="AH5">
-        <v>0.4929092500729501</v>
+        <v>0.4683113731727891</v>
       </c>
       <c r="AI5">
-        <v>0.4247956745882057</v>
+        <v>0.4556576773319411</v>
       </c>
       <c r="AJ5">
-        <v>2.947769558394978</v>
+        <v>27.60755360432521</v>
       </c>
       <c r="AK5">
-        <v>7.674350744091046</v>
+        <v>-70.84005921901179</v>
       </c>
       <c r="AL5">
-        <v>67.7</v>
+        <v>76.7</v>
       </c>
       <c r="AM5">
-        <v>67.7</v>
+        <v>76.7</v>
       </c>
       <c r="AN5">
-        <v>2.678293959093071</v>
+        <v>3.334910394265233</v>
       </c>
       <c r="AO5">
-        <v>9.1506646971935</v>
+        <v>8.58670143415906</v>
       </c>
       <c r="AP5">
-        <v>-4.16996987474235</v>
+        <v>-3.97881589354198</v>
       </c>
       <c r="AQ5">
-        <v>9.1506646971935</v>
+        <v>8.58670143415906</v>
       </c>
     </row>
     <row r="6">
@@ -1112,118 +1103,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.112</v>
+        <v>-0.073</v>
+      </c>
+      <c r="E6">
+        <v>0.119</v>
       </c>
       <c r="G6">
-        <v>0.08153554765094471</v>
+        <v>0.202538511607724</v>
       </c>
       <c r="H6">
-        <v>0.08153554765094471</v>
+        <v>0.202538511607724</v>
       </c>
       <c r="I6">
-        <v>0.07922575876564883</v>
+        <v>0.1399978303319592</v>
       </c>
       <c r="J6">
-        <v>0.05606108901875053</v>
+        <v>0.1003413020664981</v>
       </c>
       <c r="K6">
-        <v>214.2</v>
+        <v>173.2</v>
       </c>
       <c r="L6">
-        <v>0.04947567792303784</v>
+        <v>0.09394662616619658</v>
       </c>
       <c r="M6">
-        <v>31</v>
+        <v>40.8691</v>
       </c>
       <c r="N6">
-        <v>0.02067355785261754</v>
+        <v>0.03318643930166464</v>
       </c>
       <c r="O6">
-        <v>0.1447245564892624</v>
+        <v>0.2359647806004619</v>
       </c>
       <c r="P6">
-        <v>31</v>
+        <v>14.3691</v>
       </c>
       <c r="Q6">
-        <v>0.02067355785261754</v>
+        <v>0.01166796589524969</v>
       </c>
       <c r="R6">
-        <v>0.1447245564892624</v>
+        <v>0.08296247113163972</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.6484116361750075</v>
       </c>
       <c r="U6">
-        <v>1321.3</v>
+        <v>841.9</v>
       </c>
       <c r="V6">
-        <v>0.8811603867955985</v>
+        <v>0.6836378400324807</v>
       </c>
       <c r="W6">
-        <v>0.1635489043292357</v>
+        <v>0.1085621160837407</v>
       </c>
       <c r="X6">
-        <v>0.05966623046513608</v>
+        <v>0.1081693751064149</v>
       </c>
       <c r="Y6">
-        <v>0.1038826738640996</v>
+        <v>0.0003927409773257923</v>
       </c>
       <c r="Z6">
-        <v>4.657772996234534</v>
+        <v>2.046170921198668</v>
       </c>
       <c r="AA6">
-        <v>0.2611198265710366</v>
+        <v>0.2053154544836802</v>
       </c>
       <c r="AB6">
-        <v>0.04873456252033514</v>
+        <v>0.07993937004948531</v>
       </c>
       <c r="AC6">
-        <v>0.2123852640507015</v>
+        <v>0.1253760844341949</v>
       </c>
       <c r="AD6">
-        <v>626.9</v>
+        <v>942.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>626.9</v>
+        <v>942.8</v>
       </c>
       <c r="AG6">
-        <v>-694.4</v>
+        <v>100.9</v>
       </c>
       <c r="AH6">
-        <v>0.2948175319789315</v>
+        <v>0.4336108172745251</v>
       </c>
       <c r="AI6">
-        <v>0.2793672014260249</v>
+        <v>0.3624759707804691</v>
       </c>
       <c r="AJ6">
-        <v>-0.8625015526021612</v>
+        <v>0.07572800960672468</v>
       </c>
       <c r="AK6">
-        <v>-0.752573967703479</v>
+        <v>0.05735887669831163</v>
       </c>
       <c r="AL6">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="AM6">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="AN6">
-        <v>1.674412393162393</v>
+        <v>3.228767123287671</v>
       </c>
       <c r="AO6">
-        <v>11.24590163934426</v>
+        <v>7.941538461538462</v>
       </c>
       <c r="AP6">
-        <v>-1.854700854700855</v>
+        <v>0.3455479452054794</v>
       </c>
       <c r="AQ6">
-        <v>11.24590163934426</v>
+        <v>7.941538461538462</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>I.D.I. Insurance Company Ltd. (TASE:IDIN)</t>
+          <t>Harel Insurance Investments &amp; Financial Services Ltd (TASE:HARL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1243,121 +1237,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0183</v>
+        <v>-0.0289</v>
       </c>
       <c r="E7">
-        <v>0.13</v>
+        <v>0.0525</v>
       </c>
       <c r="G7">
-        <v>0.1673988789577337</v>
+        <v>0.1196821957385338</v>
       </c>
       <c r="H7">
-        <v>0.1673988789577337</v>
+        <v>0.1196821957385338</v>
       </c>
       <c r="I7">
-        <v>0.1534615967277685</v>
+        <v>0.08335139039364391</v>
       </c>
       <c r="J7">
-        <v>0.1030712216828296</v>
+        <v>0.05875337108857119</v>
       </c>
       <c r="K7">
-        <v>63</v>
+        <v>265</v>
       </c>
       <c r="L7">
-        <v>0.09544008483563096</v>
+        <v>0.06380161309738774</v>
       </c>
       <c r="M7">
-        <v>62</v>
+        <v>134.2</v>
       </c>
       <c r="N7">
-        <v>0.1156284968295412</v>
+        <v>0.071577150781375</v>
       </c>
       <c r="O7">
-        <v>0.9841269841269841</v>
+        <v>0.5064150943396226</v>
       </c>
       <c r="P7">
-        <v>62</v>
+        <v>112.3</v>
       </c>
       <c r="Q7">
-        <v>0.1156284968295412</v>
+        <v>0.05989652781481679</v>
       </c>
       <c r="R7">
-        <v>0.9841269841269841</v>
+        <v>0.4237735849056604</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>21.89999999999999</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.1631892697466467</v>
       </c>
       <c r="U7">
-        <v>92.2</v>
+        <v>1944.6</v>
       </c>
       <c r="V7">
-        <v>0.1719507646400597</v>
+        <v>1.037175316016854</v>
       </c>
       <c r="W7">
-        <v>0.2764370337867486</v>
+        <v>0.1017938770022663</v>
       </c>
       <c r="X7">
-        <v>0.05740674716254859</v>
+        <v>0.1159828016434735</v>
       </c>
       <c r="Y7">
-        <v>0.2190302866242</v>
+        <v>-0.01418892464120719</v>
       </c>
       <c r="Z7">
-        <v>2.533000767459708</v>
+        <v>1.649851042701092</v>
       </c>
       <c r="AA7">
-        <v>0.2610794836256171</v>
+        <v>0.09693431055268341</v>
       </c>
       <c r="AB7">
-        <v>0.04874688771777037</v>
+        <v>0.07955888645949483</v>
       </c>
       <c r="AC7">
-        <v>0.2123325959078467</v>
+        <v>0.01737542409318858</v>
       </c>
       <c r="AD7">
-        <v>177.5</v>
+        <v>1871.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>177.5</v>
+        <v>1871.3</v>
       </c>
       <c r="AG7">
-        <v>85.3</v>
+        <v>-73.29999999999995</v>
       </c>
       <c r="AH7">
-        <v>0.2487039372285274</v>
+        <v>0.4995195131066147</v>
       </c>
       <c r="AI7">
-        <v>0.4168623767026773</v>
+        <v>0.4479366143240137</v>
       </c>
       <c r="AJ7">
-        <v>0.1372485921158487</v>
+        <v>-0.04068605683836587</v>
       </c>
       <c r="AK7">
-        <v>0.2556954436450839</v>
+        <v>-0.03282579489476039</v>
       </c>
       <c r="AL7">
-        <v>7.23</v>
+        <v>115.7</v>
       </c>
       <c r="AM7">
-        <v>7.23</v>
+        <v>115.7</v>
       </c>
       <c r="AN7">
-        <v>1.654240447343896</v>
+        <v>4.857995846313603</v>
       </c>
       <c r="AO7">
-        <v>14.01106500691563</v>
+        <v>2.992221261884183</v>
       </c>
       <c r="AP7">
-        <v>0.7949673811742777</v>
+        <v>-0.1902907580477673</v>
       </c>
       <c r="AQ7">
-        <v>14.01106500691563</v>
+        <v>2.992221261884183</v>
       </c>
     </row>
     <row r="8">
@@ -1368,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Harel Insurance Investments &amp; Financial Services Ltd (TASE:HARL)</t>
+          <t>I.D.I. Insurance Company Ltd. (TASE:IDIN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1377,121 +1371,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.141</v>
+        <v>-0.00672</v>
       </c>
       <c r="E8">
-        <v>0.217</v>
+        <v>-0.127</v>
       </c>
       <c r="G8">
-        <v>0.0426469559540187</v>
+        <v>0.1569051580698835</v>
       </c>
       <c r="H8">
-        <v>0.0426469559540187</v>
+        <v>0.1569051580698835</v>
       </c>
       <c r="I8">
-        <v>0.05577447711427706</v>
+        <v>0.05524126455906823</v>
       </c>
       <c r="J8">
-        <v>0.0400230674427786</v>
+        <v>0.03696915397414566</v>
       </c>
       <c r="K8">
-        <v>325.1</v>
+        <v>26.1</v>
       </c>
       <c r="L8">
-        <v>0.03790192832326813</v>
+        <v>0.04342762063227953</v>
       </c>
       <c r="M8">
-        <v>84.86999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="N8">
-        <v>0.03499072356215213</v>
+        <v>0.05303030303030303</v>
       </c>
       <c r="O8">
-        <v>0.2610581359581667</v>
+        <v>0.6436781609195402</v>
       </c>
       <c r="P8">
-        <v>79.59999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="Q8">
-        <v>0.03281797567511853</v>
+        <v>0.05303030303030303</v>
       </c>
       <c r="R8">
-        <v>0.2448477391571824</v>
+        <v>0.6436781609195402</v>
       </c>
       <c r="S8">
-        <v>5.269999999999996</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.06209496877577467</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>2045.8</v>
+        <v>111.5</v>
       </c>
       <c r="V8">
-        <v>0.843454957740672</v>
+        <v>0.3519570707070707</v>
       </c>
       <c r="W8">
-        <v>0.1522217539916655</v>
+        <v>0.1051147805074507</v>
       </c>
       <c r="X8">
-        <v>0.06979056351013765</v>
+        <v>0.09896914500429518</v>
       </c>
       <c r="Y8">
-        <v>0.08243119048152786</v>
+        <v>0.006145635503155486</v>
       </c>
       <c r="Z8">
-        <v>3.807439630681818</v>
+        <v>1.801558752997602</v>
       </c>
       <c r="AA8">
-        <v>0.1523854131230865</v>
+        <v>0.0666021029330382</v>
       </c>
       <c r="AB8">
-        <v>0.0486939067473767</v>
+        <v>0.08053943380115307</v>
       </c>
       <c r="AC8">
-        <v>0.1036915063757098</v>
+        <v>-0.01393733086811487</v>
       </c>
       <c r="AD8">
-        <v>1960</v>
+        <v>155.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1960</v>
+        <v>155.8</v>
       </c>
       <c r="AG8">
-        <v>-85.79999999999995</v>
+        <v>44.30000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.446927374301676</v>
+        <v>0.3296656792213288</v>
       </c>
       <c r="AI8">
-        <v>0.4286120404994643</v>
+        <v>0.4067885117493473</v>
       </c>
       <c r="AJ8">
-        <v>-0.03667136812411846</v>
+        <v>0.1226806978676267</v>
       </c>
       <c r="AK8">
-        <v>-0.03395196074551855</v>
+        <v>0.1631675874769798</v>
       </c>
       <c r="AL8">
-        <v>88.59999999999999</v>
+        <v>6.56</v>
       </c>
       <c r="AM8">
-        <v>88.59999999999999</v>
+        <v>6.56</v>
       </c>
       <c r="AN8">
-        <v>3.824390243902439</v>
+        <v>4.005141388174808</v>
       </c>
       <c r="AO8">
-        <v>5.399548532731377</v>
+        <v>5.060975609756098</v>
       </c>
       <c r="AP8">
-        <v>-0.1674146341463414</v>
+        <v>1.138817480719795</v>
       </c>
       <c r="AQ8">
-        <v>5.399548532731377</v>
+        <v>5.060975609756098</v>
       </c>
     </row>
     <row r="9">
@@ -1511,121 +1505,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0509</v>
+        <v>0.0476</v>
       </c>
       <c r="E9">
-        <v>0.5660000000000001</v>
+        <v>-0.104</v>
       </c>
       <c r="G9">
-        <v>0.2280016447368421</v>
+        <v>0.2920497019901001</v>
       </c>
       <c r="H9">
-        <v>0.2280016447368421</v>
+        <v>0.2920497019901001</v>
       </c>
       <c r="I9">
-        <v>0.2825863486842105</v>
+        <v>0.2457824022628549</v>
       </c>
       <c r="J9">
-        <v>0.1612291798407757</v>
+        <v>0.1371808756815934</v>
       </c>
       <c r="K9">
-        <v>26.8</v>
+        <v>13.5</v>
       </c>
       <c r="L9">
-        <v>0.02754934210526316</v>
+        <v>0.01363774118597838</v>
       </c>
       <c r="M9">
-        <v>30.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N9">
-        <v>0.1155572176514585</v>
+        <v>0.07304785894206549</v>
       </c>
       <c r="O9">
-        <v>1.152985074626866</v>
+        <v>0.6444444444444444</v>
       </c>
       <c r="P9">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q9">
-        <v>0.03926701570680629</v>
+        <v>0.07304785894206549</v>
       </c>
       <c r="R9">
-        <v>0.3917910447761194</v>
+        <v>0.6444444444444444</v>
       </c>
       <c r="S9">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.6601941747572816</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>465</v>
+        <v>367.8</v>
       </c>
       <c r="V9">
-        <v>1.738967838444278</v>
+        <v>3.08816120906801</v>
       </c>
       <c r="W9">
-        <v>0.4207221350078493</v>
+        <v>0.117595818815331</v>
       </c>
       <c r="X9">
-        <v>0.3030279893967499</v>
+        <v>0.8796740847431017</v>
       </c>
       <c r="Y9">
-        <v>0.1176941456110994</v>
+        <v>-0.7620782659277707</v>
       </c>
       <c r="Z9">
-        <v>0.4827791563275435</v>
+        <v>0.4363868806207018</v>
       </c>
       <c r="AA9">
-        <v>0.07783808741891148</v>
+        <v>0.05986393441950683</v>
       </c>
       <c r="AB9">
-        <v>0.05179711762659231</v>
+        <v>0.07690316370668397</v>
       </c>
       <c r="AC9">
-        <v>0.02604096979231917</v>
+        <v>-0.01703922928717714</v>
       </c>
       <c r="AD9">
-        <v>2618.6</v>
+        <v>2825.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2618.6</v>
+        <v>2825.5</v>
       </c>
       <c r="AG9">
-        <v>2153.6</v>
+        <v>2457.7</v>
       </c>
       <c r="AH9">
-        <v>0.9073458073458073</v>
+        <v>0.9595530802146301</v>
       </c>
       <c r="AI9">
-        <v>0.8125736982560665</v>
+        <v>0.8072626496385817</v>
       </c>
       <c r="AJ9">
-        <v>0.8895497728211482</v>
+        <v>0.9537798820242162</v>
       </c>
       <c r="AK9">
-        <v>0.7809689585146504</v>
+        <v>0.7846311017463206</v>
       </c>
       <c r="AL9">
-        <v>102.9</v>
+        <v>148.3</v>
       </c>
       <c r="AM9">
-        <v>102.9</v>
+        <v>148.3</v>
       </c>
       <c r="AN9">
-        <v>9.042127071823204</v>
+        <v>10.96429957314707</v>
       </c>
       <c r="AO9">
-        <v>2.671525753158406</v>
+        <v>1.640593391773432</v>
       </c>
       <c r="AP9">
-        <v>7.436464088397789</v>
+        <v>9.537058595265812</v>
       </c>
       <c r="AQ9">
-        <v>2.671525753158406</v>
+        <v>1.640593391773432</v>
       </c>
     </row>
     <row r="10">
@@ -1636,7 +1630,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ayalon Holdings Ltd (TASE:AYAL)</t>
+          <t>Ayalon Insurance Company Ltd (TASE:AYAL)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1645,25 +1639,25 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0572</v>
+        <v>0.0567</v>
       </c>
       <c r="G10">
-        <v>-0.004724898974199565</v>
+        <v>-0.07157738095238095</v>
       </c>
       <c r="H10">
-        <v>-0.004724898974199565</v>
+        <v>-0.07157738095238095</v>
       </c>
       <c r="I10">
-        <v>-0.01647497668635375</v>
+        <v>0.03139880952380952</v>
       </c>
       <c r="J10">
-        <v>-0.01647497668635375</v>
+        <v>0.02471821175278622</v>
       </c>
       <c r="K10">
-        <v>-21.6</v>
+        <v>25.9</v>
       </c>
       <c r="L10">
-        <v>-0.0223811004041032</v>
+        <v>0.03854166666666666</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1672,7 +1666,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1681,79 +1675,79 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>169.9</v>
+        <v>169.8</v>
       </c>
       <c r="V10">
-        <v>1.119235836627141</v>
+        <v>2.519287833827893</v>
       </c>
       <c r="W10">
-        <v>-0.1071428571428572</v>
+        <v>0.1154703522068658</v>
       </c>
       <c r="X10">
-        <v>0.08970180485001819</v>
+        <v>0.201255857835152</v>
       </c>
       <c r="Y10">
-        <v>-0.1968446619928753</v>
+        <v>-0.08578550562828623</v>
       </c>
       <c r="Z10">
-        <v>2.965888137676705</v>
+        <v>2.289608177172061</v>
       </c>
       <c r="AA10">
-        <v>-0.04886293792255685</v>
+        <v>0.05659501975424989</v>
       </c>
       <c r="AB10">
-        <v>0.05082478890180957</v>
+        <v>0.07794246080950408</v>
       </c>
       <c r="AC10">
-        <v>-0.09968772682436643</v>
+        <v>-0.02134744105525419</v>
       </c>
       <c r="AD10">
-        <v>239.1</v>
+        <v>238.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>239.1</v>
+        <v>238.3</v>
       </c>
       <c r="AG10">
-        <v>69.19999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="AH10">
-        <v>0.6116653875671527</v>
+        <v>0.7795224075891396</v>
       </c>
       <c r="AI10">
-        <v>0.515412804483725</v>
+        <v>0.5744937319189971</v>
       </c>
       <c r="AJ10">
-        <v>0.3131221719457013</v>
+        <v>0.5040470934510669</v>
       </c>
       <c r="AK10">
-        <v>0.2353741496598639</v>
+        <v>0.2795918367346939</v>
       </c>
       <c r="AL10">
-        <v>14.2</v>
+        <v>10.4</v>
       </c>
       <c r="AM10">
-        <v>14.2</v>
+        <v>10.4</v>
       </c>
       <c r="AN10">
-        <v>-30.38119440914867</v>
+        <v>8.023569023569024</v>
       </c>
       <c r="AO10">
-        <v>-1.119718309859155</v>
+        <v>2.028846153846154</v>
       </c>
       <c r="AP10">
-        <v>-8.792884371029224</v>
+        <v>2.306397306397307</v>
       </c>
       <c r="AQ10">
-        <v>-1.119718309859155</v>
+        <v>2.028846153846154</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_insurance_general.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.03635</v>
+        <v>0.03950000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0478</v>
+        <v>-0.0823</v>
       </c>
       <c r="G2">
-        <v>0.1922643084350396</v>
+        <v>0.07129666315231041</v>
       </c>
       <c r="H2">
-        <v>0.1922643084350396</v>
+        <v>0.07129666315231041</v>
       </c>
       <c r="I2">
-        <v>0.1264660825878757</v>
+        <v>0.04567773494725284</v>
       </c>
       <c r="J2">
-        <v>0.08805010807863882</v>
+        <v>0.03399258467696772</v>
       </c>
       <c r="K2">
-        <v>1339.9</v>
+        <v>536.98</v>
       </c>
       <c r="L2">
-        <v>0.07556906625758568</v>
+        <v>0.01802999066569071</v>
       </c>
       <c r="M2">
-        <v>448.7691</v>
+        <v>216.67</v>
       </c>
       <c r="N2">
-        <v>0.05140833953834698</v>
+        <v>0.02324286633769578</v>
       </c>
       <c r="O2">
-        <v>0.3349273080080603</v>
+        <v>0.4034973369585459</v>
       </c>
       <c r="P2">
-        <v>384.6691</v>
+        <v>193.8</v>
       </c>
       <c r="Q2">
-        <v>0.04406542184546652</v>
+        <v>0.02078953014374598</v>
       </c>
       <c r="R2">
-        <v>0.287087917008732</v>
+        <v>0.3609072963611308</v>
       </c>
       <c r="S2">
-        <v>64.09999999999998</v>
+        <v>22.87</v>
       </c>
       <c r="T2">
-        <v>0.1428351461809647</v>
+        <v>0.1055522222735035</v>
       </c>
       <c r="U2">
-        <v>17549.1</v>
+        <v>16239.9</v>
       </c>
       <c r="V2">
-        <v>2.010321324245375</v>
+        <v>1.74210469856254</v>
       </c>
       <c r="W2">
-        <v>0.1070552992838105</v>
+        <v>0.0523169820252166</v>
       </c>
       <c r="X2">
-        <v>0.1300555468841647</v>
+        <v>0.1126309622057049</v>
       </c>
       <c r="Y2">
-        <v>-0.02300024760035416</v>
+        <v>-0.06031398018048832</v>
       </c>
       <c r="Z2">
-        <v>2.695028941919304</v>
+        <v>3.619576578109428</v>
       </c>
       <c r="AA2">
-        <v>0.1511248825181818</v>
+        <v>0.09788351145230326</v>
       </c>
       <c r="AB2">
-        <v>0.07913219930949948</v>
+        <v>0.07181547451363543</v>
       </c>
       <c r="AC2">
-        <v>0.07137575426369175</v>
+        <v>0.02549760976813654</v>
       </c>
       <c r="AD2">
-        <v>13350.4</v>
+        <v>15202.5</v>
       </c>
       <c r="AE2">
-        <v>29.77591425446982</v>
+        <v>25.69145579973799</v>
       </c>
       <c r="AF2">
-        <v>13380.17591425447</v>
+        <v>15228.19145579974</v>
       </c>
       <c r="AG2">
-        <v>-4168.924085745528</v>
+        <v>-1011.708544200261</v>
       </c>
       <c r="AH2">
-        <v>0.6051728648644756</v>
+        <v>0.6202880936067906</v>
       </c>
       <c r="AI2">
-        <v>0.5214557089984521</v>
+        <v>0.5562730118539913</v>
       </c>
       <c r="AJ2">
-        <v>-0.9141222872127174</v>
+        <v>-0.1217416440303295</v>
       </c>
       <c r="AK2">
-        <v>-0.5140362095498092</v>
+        <v>-0.09085441340564532</v>
       </c>
       <c r="AL2">
-        <v>527.76</v>
+        <v>628.39</v>
       </c>
       <c r="AM2">
-        <v>527.76</v>
+        <v>628.39</v>
       </c>
       <c r="AN2">
-        <v>5.530176877511288</v>
+        <v>9.949280104712042</v>
       </c>
       <c r="AO2">
-        <v>4.234879490677581</v>
+        <v>2.156686134406977</v>
       </c>
       <c r="AP2">
-        <v>-1.72690612888676</v>
+        <v>-0.6621129215970293</v>
       </c>
       <c r="AQ2">
-        <v>4.234879490677581</v>
+        <v>2.156686134406977</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clal Insurance Enterprises Holdings Ltd. (TASE:CLIS)</t>
+          <t>The Phoenix Holdings Ltd. (TASE:PHOE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,109 +722,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.06909999999999999</v>
+        <v>0.0703</v>
       </c>
       <c r="E3">
-        <v>-0.04769999999999999</v>
+        <v>-0.131</v>
       </c>
       <c r="G3">
-        <v>0.189383504115572</v>
+        <v>0.09861242566566067</v>
       </c>
       <c r="H3">
-        <v>0.189383504115572</v>
+        <v>0.09861242566566067</v>
       </c>
       <c r="I3">
-        <v>0.07223248782126659</v>
+        <v>0.02656601404361884</v>
       </c>
       <c r="J3">
-        <v>0.05217028942343113</v>
+        <v>0.02590930217646058</v>
       </c>
       <c r="K3">
-        <v>120.1</v>
+        <v>91.5</v>
       </c>
       <c r="L3">
-        <v>0.04034940366201915</v>
+        <v>0.01634016108005786</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03067657611481292</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.9157377049180329</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02852017280515487</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.8513661202185793</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>5.890000000000001</v>
+      </c>
+      <c r="T3">
+        <v>0.07029478458049887</v>
       </c>
       <c r="U3">
-        <v>3906.4</v>
+        <v>5651.9</v>
       </c>
       <c r="V3">
-        <v>3.138174807197944</v>
+        <v>2.069231895731127</v>
       </c>
       <c r="W3">
-        <v>0.05294013929295601</v>
+        <v>0.03390647002149263</v>
       </c>
       <c r="X3">
-        <v>0.1576888399371946</v>
+        <v>0.09987461859151509</v>
       </c>
       <c r="Y3">
-        <v>-0.1047487006442386</v>
+        <v>-0.06596814857002245</v>
       </c>
       <c r="AB3">
-        <v>0.07845188888337687</v>
+        <v>0.07077927198987505</v>
       </c>
       <c r="AD3">
-        <v>2787.3</v>
+        <v>2607.5</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>25.69145579973799</v>
       </c>
       <c r="AF3">
-        <v>2787.3</v>
+        <v>2633.191455799738</v>
       </c>
       <c r="AG3">
-        <v>-1119.1</v>
+        <v>-3018.708544200262</v>
       </c>
       <c r="AH3">
-        <v>0.6912774980779246</v>
+        <v>0.4908465961472157</v>
       </c>
       <c r="AI3">
-        <v>0.5525204670247983</v>
+        <v>0.493421967487884</v>
       </c>
       <c r="AJ3">
-        <v>-8.902943516308667</v>
+        <v>10.50685266810632</v>
       </c>
       <c r="AK3">
-        <v>-0.983132741807959</v>
+        <v>9.573824115222809</v>
       </c>
       <c r="AL3">
-        <v>69.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AM3">
-        <v>69.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AN3">
-        <v>12.33318584070797</v>
+        <v>14.34268426842684</v>
       </c>
       <c r="AO3">
-        <v>3.111432706222866</v>
+        <v>1.508403361344538</v>
       </c>
       <c r="AP3">
-        <v>-4.951769911504424</v>
+        <v>-16.60455744884632</v>
       </c>
       <c r="AQ3">
-        <v>3.111432706222866</v>
+        <v>1.508403361344538</v>
       </c>
     </row>
     <row r="4">
@@ -844,46 +847,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.122</v>
+        <v>0.0224</v>
       </c>
       <c r="E4">
-        <v>0.0478</v>
+        <v>-0.091</v>
       </c>
       <c r="G4">
-        <v>0.2365327195819856</v>
+        <v>0.04547085073106338</v>
       </c>
       <c r="H4">
-        <v>0.2365327195819856</v>
+        <v>0.04547085073106338</v>
       </c>
       <c r="I4">
-        <v>0.1429149042050261</v>
+        <v>0.02036072489346132</v>
       </c>
       <c r="J4">
-        <v>0.09471240046955132</v>
+        <v>0.01397380548771775</v>
       </c>
       <c r="K4">
-        <v>257</v>
+        <v>108</v>
       </c>
       <c r="L4">
-        <v>0.07993281910923115</v>
+        <v>0.01549653480263441</v>
       </c>
       <c r="M4">
-        <v>13.2</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N4">
-        <v>0.01099725068732817</v>
+        <v>0.006700742752176345</v>
       </c>
       <c r="O4">
-        <v>0.05136186770428015</v>
+        <v>0.07768518518518519</v>
       </c>
       <c r="P4">
-        <v>13.2</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.01099725068732817</v>
+        <v>0.006700742752176345</v>
       </c>
       <c r="R4">
-        <v>0.05136186770428015</v>
+        <v>0.07768518518518519</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,64 +895,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5076</v>
+        <v>4620.2</v>
       </c>
       <c r="V4">
-        <v>4.228942764308923</v>
+        <v>3.689960865745548</v>
       </c>
       <c r="W4">
-        <v>0.1055484824838802</v>
+        <v>0.04994912589029692</v>
       </c>
       <c r="X4">
-        <v>0.1441282921248558</v>
+        <v>0.1127833055035362</v>
       </c>
       <c r="Y4">
-        <v>-0.03857980964097554</v>
+        <v>-0.06283417961323931</v>
       </c>
       <c r="AB4">
-        <v>0.07870551215950414</v>
+        <v>0.07015477521356835</v>
       </c>
       <c r="AD4">
-        <v>2203.3</v>
+        <v>1805.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2203.3</v>
+        <v>1805.9</v>
       </c>
       <c r="AG4">
-        <v>-2872.7</v>
+        <v>-2814.3</v>
       </c>
       <c r="AH4">
-        <v>0.6473439887178282</v>
+        <v>0.5905493786788751</v>
       </c>
       <c r="AI4">
-        <v>0.5044415953111406</v>
+        <v>0.4579550641578334</v>
       </c>
       <c r="AJ4">
-        <v>1.717711073905764</v>
+        <v>1.801497887594418</v>
       </c>
       <c r="AK4">
-        <v>4.056340016944366</v>
+        <v>4.158244680851065</v>
       </c>
       <c r="AL4">
-        <v>68.5</v>
+        <v>54.8</v>
       </c>
       <c r="AM4">
-        <v>68.5</v>
+        <v>54.8</v>
       </c>
       <c r="AN4">
-        <v>4.523301170190926</v>
+        <v>12.2516960651289</v>
       </c>
       <c r="AO4">
-        <v>6.708029197080292</v>
+        <v>2.589416058394161</v>
       </c>
       <c r="AP4">
-        <v>-5.897556969821391</v>
+        <v>-19.09294436906377</v>
       </c>
       <c r="AQ4">
-        <v>6.708029197080292</v>
+        <v>2.589416058394161</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Phoenix Holdings Ltd. (TASE:PHOE)</t>
+          <t>Harel Insurance Investments &amp; Financial Services Ltd (TASE:HARL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,121 +972,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0438</v>
+        <v>0.0597</v>
       </c>
       <c r="E5">
-        <v>0.129</v>
+        <v>-0.0431</v>
       </c>
       <c r="G5">
-        <v>0.2680613582995334</v>
+        <v>0.08856586713550171</v>
       </c>
       <c r="H5">
-        <v>0.2680613582995334</v>
+        <v>0.08856586713550171</v>
       </c>
       <c r="I5">
-        <v>0.2030876817264207</v>
+        <v>0.06646364435514253</v>
       </c>
       <c r="J5">
-        <v>0.1520474608138278</v>
+        <v>0.04802021244250979</v>
       </c>
       <c r="K5">
-        <v>459.1</v>
+        <v>154.2</v>
       </c>
       <c r="L5">
-        <v>0.1400079290049099</v>
+        <v>0.02420570136883084</v>
       </c>
       <c r="M5">
-        <v>235</v>
+        <v>41.7</v>
       </c>
       <c r="N5">
-        <v>0.0878603207836393</v>
+        <v>0.02403458213256484</v>
       </c>
       <c r="O5">
-        <v>0.511871052058375</v>
+        <v>0.2704280155642024</v>
       </c>
       <c r="P5">
-        <v>219.3</v>
+        <v>26.2</v>
       </c>
       <c r="Q5">
-        <v>0.08199050360788127</v>
+        <v>0.01510086455331412</v>
       </c>
       <c r="R5">
-        <v>0.4776737094314964</v>
+        <v>0.1699092088197147</v>
       </c>
       <c r="S5">
-        <v>15.69999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="T5">
-        <v>0.06680851063829782</v>
+        <v>0.3717026378896883</v>
       </c>
       <c r="U5">
-        <v>5131.1</v>
+        <v>2909.4</v>
       </c>
       <c r="V5">
-        <v>1.918383370097581</v>
+        <v>1.676887608069164</v>
       </c>
       <c r="W5">
-        <v>0.1630326704545455</v>
+        <v>0.0672628135223555</v>
       </c>
       <c r="X5">
-        <v>0.1120416397094843</v>
+        <v>0.1124786189078736</v>
       </c>
       <c r="Y5">
-        <v>0.0509910307450612</v>
+        <v>-0.04521580538551812</v>
       </c>
       <c r="Z5">
-        <v>12.37041852415191</v>
+        <v>2.870583994232155</v>
       </c>
       <c r="AA5">
-        <v>1.880890725801639</v>
+        <v>0.1378460532370964</v>
       </c>
       <c r="AB5">
-        <v>0.0797390475895102</v>
+        <v>0.07016668396764304</v>
       </c>
       <c r="AC5">
-        <v>1.801151678212128</v>
+        <v>0.06767936926945335</v>
       </c>
       <c r="AD5">
-        <v>2326.1</v>
+        <v>2482.8</v>
       </c>
       <c r="AE5">
-        <v>29.77591425446982</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>2355.87591425447</v>
+        <v>2482.8</v>
       </c>
       <c r="AG5">
-        <v>-2775.224085745531</v>
+        <v>-426.5999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.4683113731727891</v>
+        <v>0.5886481103893025</v>
       </c>
       <c r="AI5">
-        <v>0.4556576773319411</v>
+        <v>0.5191861316158173</v>
       </c>
       <c r="AJ5">
-        <v>27.60755360432521</v>
+        <v>-0.3260470804035462</v>
       </c>
       <c r="AK5">
-        <v>-70.84005921901179</v>
+        <v>-0.2277994339723393</v>
       </c>
       <c r="AL5">
-        <v>76.7</v>
+        <v>108</v>
       </c>
       <c r="AM5">
-        <v>76.7</v>
+        <v>108</v>
       </c>
       <c r="AN5">
-        <v>3.334910394265233</v>
+        <v>5.371700562527045</v>
       </c>
       <c r="AO5">
-        <v>8.58670143415906</v>
+        <v>3.92037037037037</v>
       </c>
       <c r="AP5">
-        <v>-3.97881589354198</v>
+        <v>-0.9229770662051059</v>
       </c>
       <c r="AQ5">
-        <v>8.58670143415906</v>
+        <v>3.92037037037037</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Menora Mivtachim Holdings Ltd (TASE:MMHD)</t>
+          <t>I.D.I. Insurance Company Ltd. (TASE:IDIN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,121 +1106,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.073</v>
+        <v>0.00805</v>
       </c>
       <c r="E6">
-        <v>0.119</v>
+        <v>-0.0823</v>
       </c>
       <c r="G6">
-        <v>0.202538511607724</v>
+        <v>0.04878048780487804</v>
       </c>
       <c r="H6">
-        <v>0.202538511607724</v>
+        <v>0.04878048780487804</v>
       </c>
       <c r="I6">
-        <v>0.1399978303319592</v>
+        <v>0.07778108268887567</v>
       </c>
       <c r="J6">
-        <v>0.1003413020664981</v>
+        <v>0.05480659919002626</v>
       </c>
       <c r="K6">
-        <v>173.2</v>
+        <v>39.6</v>
       </c>
       <c r="L6">
-        <v>0.09394662616619658</v>
+        <v>0.05889351576442594</v>
       </c>
       <c r="M6">
-        <v>40.8691</v>
+        <v>21</v>
       </c>
       <c r="N6">
-        <v>0.03318643930166464</v>
+        <v>0.05063901615625754</v>
       </c>
       <c r="O6">
-        <v>0.2359647806004619</v>
+        <v>0.5303030303030303</v>
       </c>
       <c r="P6">
-        <v>14.3691</v>
+        <v>21</v>
       </c>
       <c r="Q6">
-        <v>0.01166796589524969</v>
+        <v>0.05063901615625754</v>
       </c>
       <c r="R6">
-        <v>0.08296247113163972</v>
+        <v>0.5303030303030303</v>
       </c>
       <c r="S6">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.6484116361750075</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>841.9</v>
+        <v>46.8</v>
       </c>
       <c r="V6">
-        <v>0.6836378400324807</v>
+        <v>0.1128526645768025</v>
       </c>
       <c r="W6">
-        <v>0.1085621160837407</v>
+        <v>0.1716514954486346</v>
       </c>
       <c r="X6">
-        <v>0.1081693751064149</v>
+        <v>0.08321317014330895</v>
       </c>
       <c r="Y6">
-        <v>0.0003927409773257923</v>
+        <v>0.08843832530532567</v>
       </c>
       <c r="Z6">
-        <v>2.046170921198668</v>
+        <v>1.959207459207459</v>
       </c>
       <c r="AA6">
-        <v>0.2053154544836802</v>
+        <v>0.1073774979468929</v>
       </c>
       <c r="AB6">
-        <v>0.07993937004948531</v>
+        <v>0.07224101225593557</v>
       </c>
       <c r="AC6">
-        <v>0.1253760844341949</v>
+        <v>0.03513648569095737</v>
       </c>
       <c r="AD6">
-        <v>942.8</v>
+        <v>143.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>942.8</v>
+        <v>143.8</v>
       </c>
       <c r="AG6">
-        <v>100.9</v>
+        <v>97.00000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.4336108172745251</v>
+        <v>0.2574753804834378</v>
       </c>
       <c r="AI6">
-        <v>0.3624759707804691</v>
+        <v>0.3849036402569593</v>
       </c>
       <c r="AJ6">
-        <v>0.07572800960672468</v>
+        <v>0.1895641977721322</v>
       </c>
       <c r="AK6">
-        <v>0.05735887669831163</v>
+        <v>0.2968176254589964</v>
       </c>
       <c r="AL6">
-        <v>32.5</v>
+        <v>4.79</v>
       </c>
       <c r="AM6">
-        <v>32.5</v>
+        <v>4.79</v>
       </c>
       <c r="AN6">
-        <v>3.228767123287671</v>
+        <v>2.500869565217391</v>
       </c>
       <c r="AO6">
-        <v>7.941538461538462</v>
+        <v>10.91858037578288</v>
       </c>
       <c r="AP6">
-        <v>0.3455479452054794</v>
+        <v>1.686956521739131</v>
       </c>
       <c r="AQ6">
-        <v>7.941538461538462</v>
+        <v>10.91858037578288</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1231,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Harel Insurance Investments &amp; Financial Services Ltd (TASE:HARL)</t>
+          <t>Clal Insurance Enterprises Holdings Ltd. (TASE:CLIS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,121 +1240,118 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0289</v>
+        <v>0.0457</v>
       </c>
       <c r="E7">
-        <v>0.0525</v>
+        <v>-0.0578</v>
       </c>
       <c r="G7">
-        <v>0.1196821957385338</v>
+        <v>0.02092328130189306</v>
       </c>
       <c r="H7">
-        <v>0.1196821957385338</v>
+        <v>0.02092328130189306</v>
       </c>
       <c r="I7">
-        <v>0.08335139039364391</v>
+        <v>0.02883544650008791</v>
       </c>
       <c r="J7">
-        <v>0.05875337108857119</v>
+        <v>0.01934529955069189</v>
       </c>
       <c r="K7">
-        <v>265</v>
+        <v>20.3</v>
       </c>
       <c r="L7">
-        <v>0.06380161309738774</v>
+        <v>0.003965850704280384</v>
       </c>
       <c r="M7">
-        <v>134.2</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.071577150781375</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.5064150943396226</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>112.3</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.05989652781481679</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.4237735849056604</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>21.89999999999999</v>
-      </c>
-      <c r="T7">
-        <v>0.1631892697466467</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1944.6</v>
+        <v>1993.6</v>
       </c>
       <c r="V7">
-        <v>1.037175316016854</v>
+        <v>1.485433276208926</v>
       </c>
       <c r="W7">
-        <v>0.1017938770022663</v>
+        <v>0.009064928105742609</v>
       </c>
       <c r="X7">
-        <v>0.1159828016434735</v>
+        <v>0.1505783323340114</v>
       </c>
       <c r="Y7">
-        <v>-0.01418892464120719</v>
+        <v>-0.1415134042282688</v>
       </c>
       <c r="Z7">
-        <v>1.649851042701092</v>
+        <v>4.5690440060698</v>
       </c>
       <c r="AA7">
-        <v>0.09693431055268341</v>
+        <v>0.08838952495771359</v>
       </c>
       <c r="AB7">
-        <v>0.07955888645949483</v>
+        <v>0.07253079111239787</v>
       </c>
       <c r="AC7">
-        <v>0.01737542409318858</v>
+        <v>0.01585873384531572</v>
       </c>
       <c r="AD7">
-        <v>1871.3</v>
+        <v>3815</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1871.3</v>
+        <v>3815</v>
       </c>
       <c r="AG7">
-        <v>-73.29999999999995</v>
+        <v>1821.4</v>
       </c>
       <c r="AH7">
-        <v>0.4995195131066147</v>
+        <v>0.7397568400845436</v>
       </c>
       <c r="AI7">
-        <v>0.4479366143240137</v>
+        <v>0.6301618764453254</v>
       </c>
       <c r="AJ7">
-        <v>-0.04068605683836587</v>
+        <v>0.5757547020704916</v>
       </c>
       <c r="AK7">
-        <v>-0.03282579489476039</v>
+        <v>0.4485764949266082</v>
       </c>
       <c r="AL7">
-        <v>115.7</v>
+        <v>135.5</v>
       </c>
       <c r="AM7">
-        <v>115.7</v>
+        <v>135.5</v>
       </c>
       <c r="AN7">
-        <v>4.857995846313603</v>
+        <v>21.34862898712927</v>
       </c>
       <c r="AO7">
-        <v>2.992221261884183</v>
+        <v>1.08929889298893</v>
       </c>
       <c r="AP7">
-        <v>-0.1902907580477673</v>
+        <v>10.19250139899273</v>
       </c>
       <c r="AQ7">
-        <v>2.992221261884183</v>
+        <v>1.08929889298893</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I.D.I. Insurance Company Ltd. (TASE:IDIN)</t>
+          <t>Menora Mivtachim Holdings Ltd (TASE:MMHD)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1371,121 +1371,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.00672</v>
+        <v>0.031</v>
       </c>
       <c r="E8">
-        <v>-0.127</v>
+        <v>0.0673</v>
       </c>
       <c r="G8">
-        <v>0.1569051580698835</v>
+        <v>0.07611523573830827</v>
       </c>
       <c r="H8">
-        <v>0.1569051580698835</v>
+        <v>0.07611523573830827</v>
       </c>
       <c r="I8">
-        <v>0.05524126455906823</v>
+        <v>0.06180595215432452</v>
       </c>
       <c r="J8">
-        <v>0.03696915397414566</v>
+        <v>0.04288435339422964</v>
       </c>
       <c r="K8">
-        <v>26.1</v>
+        <v>118.7</v>
       </c>
       <c r="L8">
-        <v>0.04342762063227953</v>
+        <v>0.03766101910019671</v>
       </c>
       <c r="M8">
-        <v>16.8</v>
+        <v>60.48</v>
       </c>
       <c r="N8">
-        <v>0.05303030303030303</v>
+        <v>0.0364403205398566</v>
       </c>
       <c r="O8">
-        <v>0.6436781609195402</v>
+        <v>0.509519797809604</v>
       </c>
       <c r="P8">
-        <v>16.8</v>
+        <v>59</v>
       </c>
       <c r="Q8">
-        <v>0.05303030303030303</v>
+        <v>0.03554859311923841</v>
       </c>
       <c r="R8">
-        <v>0.6436781609195402</v>
+        <v>0.4970513900589722</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.479999999999997</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.02447089947089942</v>
       </c>
       <c r="U8">
-        <v>111.5</v>
+        <v>773.9</v>
       </c>
       <c r="V8">
-        <v>0.3519570707070707</v>
+        <v>0.466289088389468</v>
       </c>
       <c r="W8">
-        <v>0.1051147805074507</v>
+        <v>0.07374502982107356</v>
       </c>
       <c r="X8">
-        <v>0.09896914500429518</v>
+        <v>0.09000106732286059</v>
       </c>
       <c r="Y8">
-        <v>0.006145635503155486</v>
+        <v>-0.01625603750178703</v>
       </c>
       <c r="Z8">
-        <v>1.801558752997602</v>
+        <v>1.842619117217189</v>
       </c>
       <c r="AA8">
-        <v>0.0666021029330382</v>
+        <v>0.07901952939370535</v>
       </c>
       <c r="AB8">
-        <v>0.08053943380115307</v>
+        <v>0.07150919627494529</v>
       </c>
       <c r="AC8">
-        <v>-0.01393733086811487</v>
+        <v>0.007510333118760065</v>
       </c>
       <c r="AD8">
-        <v>155.8</v>
+        <v>992.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>155.8</v>
+        <v>992.9</v>
       </c>
       <c r="AG8">
-        <v>44.30000000000001</v>
+        <v>219</v>
       </c>
       <c r="AH8">
-        <v>0.3296656792213288</v>
+        <v>0.3743119957777275</v>
       </c>
       <c r="AI8">
-        <v>0.4067885117493473</v>
+        <v>0.3696850100528706</v>
       </c>
       <c r="AJ8">
-        <v>0.1226806978676267</v>
+        <v>0.1165699685953053</v>
       </c>
       <c r="AK8">
-        <v>0.1631675874769798</v>
+        <v>0.1145457398399498</v>
       </c>
       <c r="AL8">
-        <v>6.56</v>
+        <v>50.6</v>
       </c>
       <c r="AM8">
-        <v>6.56</v>
+        <v>50.6</v>
       </c>
       <c r="AN8">
-        <v>4.005141388174808</v>
+        <v>4.374008810572687</v>
       </c>
       <c r="AO8">
-        <v>5.060975609756098</v>
+        <v>3.849802371541502</v>
       </c>
       <c r="AP8">
-        <v>1.138817480719795</v>
+        <v>0.9647577092511013</v>
       </c>
       <c r="AQ8">
-        <v>5.060975609756098</v>
+        <v>3.849802371541502</v>
       </c>
     </row>
     <row r="9">
@@ -1505,46 +1505,43 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0476</v>
-      </c>
-      <c r="E9">
-        <v>-0.104</v>
+        <v>0.0542</v>
       </c>
       <c r="G9">
-        <v>0.2920497019901001</v>
+        <v>0.2274549098196393</v>
       </c>
       <c r="H9">
-        <v>0.2920497019901001</v>
+        <v>0.2274549098196393</v>
       </c>
       <c r="I9">
-        <v>0.2457824022628549</v>
+        <v>0.2219894334122791</v>
       </c>
       <c r="J9">
-        <v>0.1371808756815934</v>
+        <v>0.1109947167061396</v>
       </c>
       <c r="K9">
-        <v>13.5</v>
+        <v>-4.95</v>
       </c>
       <c r="L9">
-        <v>0.01363774118597838</v>
+        <v>-0.004509018036072144</v>
       </c>
       <c r="M9">
-        <v>8.699999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="N9">
-        <v>0.07304785894206549</v>
+        <v>0.0127555988315482</v>
       </c>
       <c r="O9">
-        <v>0.6444444444444444</v>
+        <v>-0.2646464646464646</v>
       </c>
       <c r="P9">
-        <v>8.699999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="Q9">
-        <v>0.07304785894206549</v>
+        <v>0.0127555988315482</v>
       </c>
       <c r="R9">
-        <v>0.6444444444444444</v>
+        <v>-0.2646464646464646</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1553,73 +1550,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>367.8</v>
+        <v>168.9</v>
       </c>
       <c r="V9">
-        <v>3.08816120906801</v>
+        <v>1.644595910418695</v>
       </c>
       <c r="W9">
-        <v>0.117595818815331</v>
+        <v>-0.03730218538055766</v>
       </c>
       <c r="X9">
-        <v>0.8796740847431017</v>
+        <v>0.9032273954309187</v>
       </c>
       <c r="Y9">
-        <v>-0.7620782659277707</v>
+        <v>-0.9405295808114763</v>
       </c>
       <c r="Z9">
-        <v>0.4363868806207018</v>
+        <v>0.4237955528103768</v>
       </c>
       <c r="AA9">
-        <v>0.05986393441950683</v>
+        <v>0.04703906732550958</v>
       </c>
       <c r="AB9">
-        <v>0.07690316370668397</v>
+        <v>0.07212175275232557</v>
       </c>
       <c r="AC9">
-        <v>-0.01703922928717714</v>
+        <v>-0.02508268542681599</v>
       </c>
       <c r="AD9">
-        <v>2825.5</v>
+        <v>3155.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2825.5</v>
+        <v>3155.7</v>
       </c>
       <c r="AG9">
-        <v>2457.7</v>
+        <v>2986.8</v>
       </c>
       <c r="AH9">
-        <v>0.9595530802146301</v>
+        <v>0.9684814632948687</v>
       </c>
       <c r="AI9">
-        <v>0.8072626496385817</v>
+        <v>0.825840050245996</v>
       </c>
       <c r="AJ9">
-        <v>0.9537798820242162</v>
+        <v>0.9667583751416088</v>
       </c>
       <c r="AK9">
-        <v>0.7846311017463206</v>
+        <v>0.8177860526243736</v>
       </c>
       <c r="AL9">
-        <v>148.3</v>
+        <v>166</v>
       </c>
       <c r="AM9">
-        <v>148.3</v>
+        <v>166</v>
       </c>
       <c r="AN9">
-        <v>10.96429957314707</v>
+        <v>12.17476851851852</v>
       </c>
       <c r="AO9">
-        <v>1.640593391773432</v>
+        <v>1.468072289156626</v>
       </c>
       <c r="AP9">
-        <v>9.537058595265812</v>
+        <v>11.52314814814815</v>
       </c>
       <c r="AQ9">
-        <v>1.640593391773432</v>
+        <v>1.468072289156626</v>
       </c>
     </row>
     <row r="10">
@@ -1639,25 +1636,28 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0567</v>
+        <v>0.0333</v>
+      </c>
+      <c r="E10">
+        <v>-0.083</v>
       </c>
       <c r="G10">
-        <v>-0.07157738095238095</v>
+        <v>0.07551401869158879</v>
       </c>
       <c r="H10">
-        <v>-0.07157738095238095</v>
+        <v>0.07551401869158879</v>
       </c>
       <c r="I10">
-        <v>0.03139880952380952</v>
+        <v>0.009894080996884736</v>
       </c>
       <c r="J10">
-        <v>0.02471821175278622</v>
+        <v>0.009894080996884736</v>
       </c>
       <c r="K10">
-        <v>25.9</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L10">
-        <v>0.03854166666666666</v>
+        <v>0.012</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1681,73 +1681,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>169.8</v>
+        <v>75.2</v>
       </c>
       <c r="V10">
-        <v>2.519287833827893</v>
+        <v>0.8920521945432978</v>
       </c>
       <c r="W10">
-        <v>0.1154703522068658</v>
+        <v>0.05468483816013629</v>
       </c>
       <c r="X10">
-        <v>0.201255857835152</v>
+        <v>0.1375380021879288</v>
       </c>
       <c r="Y10">
-        <v>-0.08578550562828623</v>
+        <v>-0.08285316402779254</v>
       </c>
       <c r="Z10">
-        <v>2.289608177172061</v>
+        <v>3.280866721177433</v>
       </c>
       <c r="AA10">
-        <v>0.05659501975424989</v>
+        <v>0.03246116107931317</v>
       </c>
       <c r="AB10">
-        <v>0.07794246080950408</v>
+        <v>0.07259772227656544</v>
       </c>
       <c r="AC10">
-        <v>-0.02134744105525419</v>
+        <v>-0.04013656119725227</v>
       </c>
       <c r="AD10">
-        <v>238.3</v>
+        <v>198.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>238.3</v>
+        <v>198.9</v>
       </c>
       <c r="AG10">
-        <v>68.5</v>
+        <v>123.7</v>
       </c>
       <c r="AH10">
-        <v>0.7795224075891396</v>
+        <v>0.7023305084745763</v>
       </c>
       <c r="AI10">
-        <v>0.5744937319189971</v>
+        <v>0.5252178505413255</v>
       </c>
       <c r="AJ10">
-        <v>0.5040470934510669</v>
+        <v>0.5947115384615385</v>
       </c>
       <c r="AK10">
-        <v>0.2795918367346939</v>
+        <v>0.4075782537067545</v>
       </c>
       <c r="AL10">
-        <v>10.4</v>
+        <v>13.5</v>
       </c>
       <c r="AM10">
-        <v>10.4</v>
+        <v>13.5</v>
       </c>
       <c r="AN10">
-        <v>8.023569023569024</v>
+        <v>14.00704225352113</v>
       </c>
       <c r="AO10">
-        <v>2.028846153846154</v>
+        <v>0.5881481481481482</v>
       </c>
       <c r="AP10">
-        <v>2.306397306397307</v>
+        <v>8.711267605633804</v>
       </c>
       <c r="AQ10">
-        <v>2.028846153846154</v>
+        <v>0.5881481481481482</v>
       </c>
     </row>
   </sheetData>
